--- a/testdata/generated_employee_details.xlsx
+++ b/testdata/generated_employee_details.xlsx
@@ -478,13 +478,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LLLA30</v>
+        <v>LEYH67</v>
       </c>
       <c r="B2" t="str">
-        <v>Vickie</v>
+        <v>Gertrude</v>
       </c>
       <c r="C2" t="str">
-        <v>Swaniawski</v>
+        <v>Stracke</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -493,13 +493,13 @@
         <v>8976589760</v>
       </c>
       <c r="F2" t="str">
-        <v>Karl.Jones@hotmail.com</v>
+        <v>Kari.Kling@gmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>UAN123456</v>
       </c>
       <c r="H2" t="str">
-        <v>Roma.Erdman5@hotmail.com</v>
+        <v>Marsha31@gmail.com</v>
       </c>
       <c r="I2" t="str">
         <v>32</v>
@@ -555,13 +555,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LCXV65</v>
+        <v>LCLG47</v>
       </c>
       <c r="B3" t="str">
-        <v>Jackie</v>
+        <v>Arturo</v>
       </c>
       <c r="C3" t="str">
-        <v>Koepp</v>
+        <v>Lynch</v>
       </c>
       <c r="D3" t="str">
         <v>Male</v>
@@ -570,13 +570,13 @@
         <v>8976589760</v>
       </c>
       <c r="F3" t="str">
-        <v>Noah.DAmore50@gmail.com</v>
+        <v>Karen78@gmail.com</v>
       </c>
       <c r="G3" t="str">
         <v>UAN123456</v>
       </c>
       <c r="H3" t="str">
-        <v>Marguerite.Terry80@hotmail.com</v>
+        <v>Declan41@gmail.com</v>
       </c>
       <c r="I3" t="str">
         <v>32</v>
